--- a/data/Car_Usage.xlsx
+++ b/data/Car_Usage.xlsx
@@ -398,7 +398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.26953125" customWidth="1" min="2" max="2"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16:60</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1101,6 +1101,41 @@
     <row r="21">
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>P1 - Weld</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ravi</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>tkm2026/7788</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Car_Usage.xlsx
+++ b/data/Car_Usage.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
